--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9739" uniqueCount="1755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9891" uniqueCount="1831">
   <si>
     <t>Result</t>
   </si>
@@ -5336,6 +5336,234 @@
   </si>
   <si>
     <t>Wed Jun 10 20:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 14:46:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 14:50:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 14:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 14:55:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 14:58:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:00:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:03:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:05:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:07:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:10:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:12:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:15:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:17:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:18:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:22:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:23:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:26:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:27:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:29:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:30:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:31:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:33:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:34:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:39:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:41:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:43:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:44:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:47:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:49:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:52:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 15:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:03:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:06:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:08:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:11:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:13:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:20:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:23:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:25:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:28:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:30:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:32:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:33:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:38:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:46:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:47:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:49:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:52:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:55:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 16:58:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:01:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:03:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:06:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:08:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:10:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:16:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:19:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:22:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:26:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:29:46 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -5751,7 +5979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
@@ -5863,10 +6091,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>1737</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -5901,10 +6129,10 @@
       </c>
     </row>
     <row ht="28.8" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="1">
         <v>1738</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5981,10 +6209,10 @@
       </c>
     </row>
     <row ht="28.8" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="1">
         <v>1739</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -6061,10 +6289,10 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="1">
         <v>1740</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -6129,10 +6357,10 @@
       </c>
     </row>
     <row ht="28.8" r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="1">
         <v>1741</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -6167,10 +6395,10 @@
       </c>
     </row>
     <row ht="28.8" r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="1">
         <v>1742</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -6247,10 +6475,10 @@
       </c>
     </row>
     <row ht="28.8" r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="1">
         <v>1743</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -6327,10 +6555,10 @@
       </c>
     </row>
     <row ht="43.2" r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="1">
         <v>1744</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -6405,7 +6633,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A771A143-9840-4DFA-B0E0-D15CFA2A9A1E}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -6495,10 +6723,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1607</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6579,10 +6807,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1608</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6669,7 +6897,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AA9D37-D04B-4587-A172-B9ADC89C694F}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -6759,10 +6987,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1615</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -6841,10 +7069,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1616</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6929,7 +7157,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AB254A-353D-44A3-9E69-985EFBB297E1}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -7022,10 +7250,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1611</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7106,10 +7334,10 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1612</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7196,7 +7424,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313069EA-AC8D-4820-8DAC-508C0AEC1D04}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -7289,10 +7517,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1619</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -7373,10 +7601,10 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1620</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7463,7 +7691,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -7553,11 +7781,11 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>1697</v>
+      <c r="B2" t="s" s="0">
+        <v>1807</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -7634,11 +7862,11 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>1698</v>
+      <c r="B3" t="s" s="0">
+        <v>1808</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -7687,11 +7915,11 @@
       <c r="AA3" s="1"/>
     </row>
     <row ht="43.2" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>1699</v>
+      <c r="B4" t="s" s="0">
+        <v>1809</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -7768,11 +7996,11 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>1700</v>
+      <c r="B5" t="s" s="0">
+        <v>1810</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -7832,7 +8060,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41878333-4EED-4FEF-A1C8-5BD85093D0BA}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -7922,11 +8150,11 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>1705</v>
+      <c r="B2" t="s" s="0">
+        <v>1821</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7976,11 +8204,11 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>1706</v>
+      <c r="B3" t="s" s="0">
+        <v>1822</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -8058,11 +8286,11 @@
       </c>
     </row>
     <row ht="72" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>1707</v>
+      <c r="B4" t="s" s="0">
+        <v>1823</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -8112,11 +8340,11 @@
       <c r="AB4" s="1"/>
     </row>
     <row ht="72" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>1708</v>
+      <c r="B5" t="s" s="0">
+        <v>1824</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -8200,7 +8428,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE00763E-41D4-4301-BDED-25AE7808C112}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -8296,11 +8524,11 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1719</v>
+      <c r="A2" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>1829</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -8383,11 +8611,11 @@
       </c>
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1720</v>
+      <c r="A3" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>1830</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -8444,10 +8672,10 @@
       <c r="AC3" s="1"/>
     </row>
     <row ht="72" r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1721</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -8531,10 +8759,10 @@
       </c>
     </row>
     <row ht="86.4" r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1722</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -8598,7 +8826,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD743872-79BE-45C8-95F1-7462ADBFBB33}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -8694,10 +8922,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1727</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8781,10 +9009,10 @@
       </c>
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1728</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -8842,10 +9070,10 @@
       <c r="AC3" s="1"/>
     </row>
     <row ht="72" r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1729</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -8929,10 +9157,10 @@
       </c>
     </row>
     <row ht="86.4" r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1730</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -8996,7 +9224,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A88FA1-BB65-44BB-BC88-0BCE20A6C9BB}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -9086,11 +9314,11 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>1701</v>
+      <c r="B2" t="s" s="0">
+        <v>1817</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9140,11 +9368,11 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>1702</v>
+      <c r="B3" t="s" s="0">
+        <v>1818</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -9222,11 +9450,11 @@
       </c>
     </row>
     <row ht="72" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>1703</v>
+      <c r="B4" t="s" s="0">
+        <v>1819</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -9276,11 +9504,11 @@
       <c r="AB4" s="1"/>
     </row>
     <row ht="72" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>1704</v>
+      <c r="B5" t="s" s="0">
+        <v>1820</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -9364,7 +9592,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -9454,11 +9682,11 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>1687</v>
+      <c r="B2" t="s" s="0">
+        <v>1803</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -9535,11 +9763,11 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>1688</v>
+      <c r="B3" t="s" s="0">
+        <v>1804</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -9588,11 +9816,11 @@
       <c r="AA3" s="1"/>
     </row>
     <row ht="43.2" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>1689</v>
+      <c r="B4" t="s" s="0">
+        <v>1805</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -9669,11 +9897,11 @@
       </c>
     </row>
     <row ht="43.2" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>1690</v>
+      <c r="B5" t="s" s="0">
+        <v>1806</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -9733,7 +9961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
@@ -9848,11 +10076,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1709</v>
+      <c r="A2" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>1791</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -9931,11 +10159,11 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1710</v>
+      <c r="A3" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>1792</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -9969,11 +10197,11 @@
       </c>
     </row>
     <row ht="28.8" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1711</v>
+      <c r="A4" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>1793</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -10040,11 +10268,11 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1712</v>
+      <c r="A5" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>1794</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -10123,11 +10351,11 @@
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1713</v>
+      <c r="A6" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>1795</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -10161,11 +10389,11 @@
       </c>
     </row>
     <row ht="28.8" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1714</v>
+      <c r="A7" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>1796</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -10239,7 +10467,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C03D0C9-5AB6-4662-AC40-046602184333}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:30" x14ac:dyDescent="0.3">
@@ -10335,11 +10563,11 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1723</v>
+      <c r="A2" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>1825</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -10422,11 +10650,11 @@
       </c>
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1724</v>
+      <c r="A3" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>1826</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -10483,11 +10711,11 @@
       <c r="AC3" s="1"/>
     </row>
     <row ht="72" r="4" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1725</v>
+      <c r="A4" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>1827</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -10570,11 +10798,11 @@
       </c>
     </row>
     <row ht="86.4" r="5" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1726</v>
+      <c r="A5" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>1828</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -10637,7 +10865,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EA1570-2F70-4A5F-BF7E-DF89621604FD}">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -10730,7 +10958,7 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10814,7 +11042,7 @@
       </c>
     </row>
     <row ht="86.4" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -11010,7 +11238,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A79848-7E61-44B5-97E7-0F536B72AE4E}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -11100,10 +11328,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1627</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11182,10 +11410,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1628</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11270,7 +11498,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -11360,10 +11588,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1629</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11441,10 +11669,10 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1630</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11533,7 +11761,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4062C9F-5A44-415A-A7E8-078A7E971ECD}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -11632,10 +11860,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1631</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11722,10 +11950,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1632</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11809,7 +12037,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04751CF-732C-4149-ABDB-2383247CAD77}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -11908,10 +12136,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1633</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11998,10 +12226,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1634</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12085,7 +12313,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19564025-DA14-4B1C-B957-0CD06F0D7994}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -12184,10 +12412,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1639</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12274,10 +12502,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1640</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12361,7 +12589,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD57A086-2829-4F5A-903D-49E7780DD68D}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" customWidth="true" width="16.33203125" collapsed="true"/>
@@ -12455,10 +12683,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1635</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12537,10 +12765,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1636</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12624,7 +12852,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -12714,10 +12942,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1637</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -12795,10 +13023,10 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1638</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -12887,7 +13115,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFD3F70-9018-4826-9ABF-5AB54B85F996}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -12986,10 +13214,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1641</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13076,10 +13304,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1642</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13163,7 +13391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
@@ -13278,11 +13506,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1731</v>
+      <c r="A2" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>1797</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -13361,11 +13589,11 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1732</v>
+      <c r="A3" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>1798</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -13399,11 +13627,11 @@
       </c>
     </row>
     <row ht="28.8" r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1733</v>
+      <c r="A4" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>1799</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -13470,11 +13698,11 @@
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1734</v>
+      <c r="A5" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>1800</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -13553,11 +13781,11 @@
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1735</v>
+      <c r="A6" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>1801</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -13591,11 +13819,11 @@
       </c>
     </row>
     <row ht="28.8" r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1736</v>
+      <c r="A7" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>1802</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -13669,7 +13897,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A9304B-BE96-4389-93F5-881CE531B763}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -13759,10 +13987,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1751</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -13815,10 +14043,10 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1752</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -13871,10 +14099,10 @@
       <c r="AB3" s="2"/>
     </row>
     <row ht="72" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1753</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -13927,10 +14155,10 @@
       <c r="AB4" s="1"/>
     </row>
     <row ht="72" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1754</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -13989,7 +14217,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B9C217-1BF0-431A-9AA8-3A32A964B4CD}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -14088,10 +14316,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1679</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14154,10 +14382,10 @@
       <c r="AD2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1680</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14193,13 +14421,13 @@
       <c r="S3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" t="s" s="0">
         <v>84</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="0">
         <v>1</v>
       </c>
       <c r="W3" s="1">
@@ -14220,10 +14448,10 @@
       <c r="AD3" s="1"/>
     </row>
     <row ht="72" r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1681</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -14286,10 +14514,10 @@
       <c r="AD4" s="1"/>
     </row>
     <row ht="72" r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1682</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -14325,13 +14553,13 @@
       <c r="S5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" t="s" s="0">
         <v>84</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="0">
         <v>1</v>
       </c>
       <c r="W5" s="1">
@@ -14358,7 +14586,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15C6E0B-3928-44AA-AEF4-FBE07F9F5942}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -14457,10 +14685,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1683</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14523,10 +14751,10 @@
       <c r="AD2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1684</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14562,13 +14790,13 @@
       <c r="S3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" t="s" s="0">
         <v>84</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="0">
         <v>2</v>
       </c>
       <c r="W3" s="1">
@@ -14589,10 +14817,10 @@
       <c r="AD3" s="1"/>
     </row>
     <row ht="72" r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1685</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -14655,10 +14883,10 @@
       <c r="AD4" s="1"/>
     </row>
     <row ht="72" r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1686</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -14694,13 +14922,13 @@
       <c r="S5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" t="s" s="0">
         <v>84</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="0">
         <v>2</v>
       </c>
       <c r="W5" s="1">
@@ -14727,7 +14955,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -14817,10 +15045,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1671</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -14874,10 +15102,10 @@
       <c r="AA2" s="1"/>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1672</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -14931,10 +15159,10 @@
       <c r="AA3" s="1"/>
     </row>
     <row ht="43.2" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>1673</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -14988,10 +15216,10 @@
       <c r="AA4" s="1"/>
     </row>
     <row ht="43.2" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>1674</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -15056,7 +15284,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD0BECA-198B-4690-8CF3-A2199F4B543B}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -15146,10 +15374,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1659</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15197,10 +15425,10 @@
       <c r="AA2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1660</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15254,7 +15482,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0893653-4D6E-4E06-95C2-AA32E63A578A}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -15353,10 +15581,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1661</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15413,10 +15641,10 @@
       <c r="AD2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1662</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15479,7 +15707,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508EF0D1-65BE-4C3B-8DB2-F5B51668E3FA}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -15578,10 +15806,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1663</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15638,10 +15866,10 @@
       <c r="AD2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1664</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15704,7 +15932,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B1E44C-ACC0-46A9-ADFB-04E3A56B3216}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -15794,10 +16022,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1657</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -15844,10 +16072,10 @@
       <c r="AB2" s="1"/>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1658</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -15902,7 +16130,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD3CF7C-C466-4C10-9D8E-94B88363961A}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -15992,10 +16220,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1645</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -16052,10 +16280,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1646</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -16120,7 +16348,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F043AE-8D22-4522-B277-A3F8143D1C61}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -16219,10 +16447,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1649</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -16285,10 +16513,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1650</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -16357,7 +16585,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
@@ -16472,11 +16700,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>1691</v>
+      <c r="B2" t="s" s="1">
+        <v>1811</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16552,11 +16780,11 @@
       </c>
     </row>
     <row ht="28.8" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>1692</v>
+      <c r="B3" t="s" s="1">
+        <v>1812</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -16590,11 +16818,11 @@
       </c>
     </row>
     <row ht="43.2" r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>1693</v>
+      <c r="B4" t="s" s="1">
+        <v>1813</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>69</v>
@@ -16655,11 +16883,11 @@
       </c>
     </row>
     <row ht="28.8" r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>1694</v>
+      <c r="B5" t="s" s="1">
+        <v>1814</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -16735,11 +16963,11 @@
       </c>
     </row>
     <row ht="28.8" r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>1695</v>
+      <c r="B6" t="s" s="1">
+        <v>1815</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>68</v>
@@ -16773,11 +17001,11 @@
       </c>
     </row>
     <row ht="43.2" r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>1696</v>
+      <c r="B7" t="s" s="1">
+        <v>1816</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>69</v>
@@ -16845,7 +17073,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -16935,10 +17163,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1647</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -16992,10 +17220,10 @@
       </c>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1648</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -17060,7 +17288,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D69F64-0838-4A1D-A1AD-91EF5273BDCB}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -17159,10 +17387,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1651</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17225,10 +17453,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1652</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -17297,7 +17525,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A32E7FC-2B9D-4ACF-971E-602A35B77002}">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -17396,10 +17624,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1656</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17468,7 +17696,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F3F3AF-F561-446D-9C6A-79A3AF94AE18}">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:31" x14ac:dyDescent="0.3">
@@ -17567,10 +17795,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1655</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17639,7 +17867,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00FDC39-BDF2-4377-92A2-1FC9690FDA62}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -17729,10 +17957,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1653</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17795,7 +18023,7 @@
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -17885,10 +18113,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1654</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17953,7 +18181,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C292913-F503-43A9-973A-22B728942B3F}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -18043,10 +18271,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1623</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -18125,10 +18353,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1624</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -18213,7 +18441,7 @@
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF3FD29C-0D01-442A-B539-C7DB6D779E85}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" customWidth="true" width="54.6640625" collapsed="true"/>
@@ -18306,10 +18534,10 @@
       </c>
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1745</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -18388,10 +18616,10 @@
       </c>
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1746</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -18477,7 +18705,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -18567,10 +18795,10 @@
       </c>
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1643</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -18620,10 +18848,10 @@
       <c r="AA2" s="1"/>
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1644</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -18684,7 +18912,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5489C7-A3C1-4624-93CA-9485979F3AC1}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -18774,10 +19002,10 @@
       </c>
     </row>
     <row ht="115.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1609</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -18845,10 +19073,10 @@
       </c>
     </row>
     <row ht="115.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1610</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -18922,7 +19150,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B2D42D-4180-4EF8-8D50-E71E1F3080A1}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -19012,10 +19240,10 @@
       </c>
     </row>
     <row ht="115.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1617</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -19083,10 +19311,10 @@
       </c>
     </row>
     <row ht="115.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1618</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -19160,7 +19388,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9E142F-4A51-4D5A-B6C1-BDE7AA487EEE}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -19253,10 +19481,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1613</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -19337,10 +19565,10 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1614</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -19427,7 +19655,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6B170A-199C-481C-A301-EFB2F4847854}">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -19520,10 +19748,10 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>1621</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -19604,10 +19832,10 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>1622</v>
       </c>
       <c r="C3" s="1" t="s">

--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9891" uniqueCount="1831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10419" uniqueCount="2095">
   <si>
     <t>Result</t>
   </si>
@@ -5564,6 +5564,798 @@
   </si>
   <si>
     <t>Wed Aug 19 17:29:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:11:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:18:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:21:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:24:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:27:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:30:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:33:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:36:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:38:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:41:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:46:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:49:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:52:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:53:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:54:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:57:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:58:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 00:59:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:01:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:02:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:03:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:06:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:07:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:09:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:10:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:11:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:18:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:21:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:29:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:36:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:39:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:43:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:46:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:50:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:54:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 01:58:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:01:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:05:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:08:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:13:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:14:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:16:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:17:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:18:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:19:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:20:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:21:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:22:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:23:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:24:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:26:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:27:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:28:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:33:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:39:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:42:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:06:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:08:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:09:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:13:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:18:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:52:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:53:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:02:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:06:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:15:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:16:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:17:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:18:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:19:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:20:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:22:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:25:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:27:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:33:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:35:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:36:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:37:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:39:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:44:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:46:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:47:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:48:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:49:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:52:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:56:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:58:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:01:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:02:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:05:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:07:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:08:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:10:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:11:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:14:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:16:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 22:56:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:01:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:04:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:07:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:16:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:22:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:25:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:28:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:34:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:35:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:37:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:39:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:42:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:45:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:46:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:49:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:51:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:52:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:53:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:55:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 23:58:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:00:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:04:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:06:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:10:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:17:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:25:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:29:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:32:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:36:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:39:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:49:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 00:57:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:01:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:05:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:09:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:10:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:11:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:12:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:14:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:16:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:18:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:19:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:22:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:24:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:26:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:27:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:31:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:33:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:42:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:45:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:08:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:12:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:13:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:15:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:18:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:56:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:57:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:58:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:03:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:27:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:28:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:30:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:35:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:37:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:40:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:44:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:45:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:46:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:48:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:51:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:57:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:59:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:00:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:01:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:04:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:05:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:13:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:15:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:16:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:18:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:20:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:22:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:23:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:26:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:27:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:31:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:34:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:37:02 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -6095,7 +6887,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1737</v>
+        <v>2013</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6133,7 +6925,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1738</v>
+        <v>2014</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -6213,7 +7005,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1739</v>
+        <v>2015</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -6293,7 +7085,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1740</v>
+        <v>2016</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>37</v>
@@ -6361,7 +7153,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1741</v>
+        <v>2017</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -6399,7 +7191,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1742</v>
+        <v>2018</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -6479,7 +7271,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>1743</v>
+        <v>2019</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -6559,7 +7351,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>1744</v>
+        <v>2020</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>37</v>
@@ -6727,7 +7519,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1607</v>
+        <v>2037</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -6811,7 +7603,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1608</v>
+        <v>2038</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -6991,7 +7783,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1615</v>
+        <v>2045</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -7073,7 +7865,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1616</v>
+        <v>2046</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -7251,10 +8043,10 @@
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1611</v>
+        <v>2041</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -7335,10 +8127,10 @@
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1612</v>
+        <v>2042</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -7518,10 +8310,10 @@
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1619</v>
+        <v>2049</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -7602,10 +8394,10 @@
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1620</v>
+        <v>2050</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -7785,7 +8577,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1807</v>
+        <v>1979</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -7866,7 +8658,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1808</v>
+        <v>1980</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -7919,7 +8711,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1809</v>
+        <v>1981</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -8000,7 +8792,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1810</v>
+        <v>1982</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -8154,7 +8946,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1821</v>
+        <v>1993</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8208,7 +9000,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1822</v>
+        <v>1994</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -8290,7 +9082,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1823</v>
+        <v>1995</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -8344,7 +9136,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1824</v>
+        <v>1996</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -8528,7 +9320,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1829</v>
+        <v>2001</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -8615,7 +9407,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1830</v>
+        <v>2002</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -8673,10 +9465,10 @@
     </row>
     <row ht="72" r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1721</v>
+        <v>2003</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -8760,10 +9552,10 @@
     </row>
     <row ht="86.4" r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1722</v>
+        <v>2004</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -8923,10 +9715,10 @@
     </row>
     <row ht="72" r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1727</v>
+        <v>2005</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -9010,10 +9802,10 @@
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1728</v>
+        <v>2006</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -9071,10 +9863,10 @@
     </row>
     <row ht="72" r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1729</v>
+        <v>2007</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -9158,10 +9950,10 @@
     </row>
     <row ht="86.4" r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1730</v>
+        <v>2008</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -9318,7 +10110,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1817</v>
+        <v>1989</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9372,7 +10164,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1818</v>
+        <v>1990</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -9454,7 +10246,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1819</v>
+        <v>1991</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -9508,7 +10300,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1820</v>
+        <v>1992</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -9686,7 +10478,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1803</v>
+        <v>1975</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -9767,7 +10559,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1804</v>
+        <v>1976</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -9820,7 +10612,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1805</v>
+        <v>1977</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -9901,7 +10693,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1806</v>
+        <v>1978</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -10080,7 +10872,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1791</v>
+        <v>1963</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -10163,7 +10955,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1792</v>
+        <v>1964</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -10201,7 +10993,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1793</v>
+        <v>1965</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -10272,7 +11064,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1794</v>
+        <v>1966</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -10355,7 +11147,7 @@
         <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1795</v>
+        <v>1967</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -10393,7 +11185,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1796</v>
+        <v>1968</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -10567,7 +11359,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1825</v>
+        <v>2009</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -10654,7 +11446,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1826</v>
+        <v>2010</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -10715,7 +11507,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1827</v>
+        <v>2011</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -10802,7 +11594,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1828</v>
+        <v>2012</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -11332,7 +12124,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1627</v>
+        <v>2057</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -11414,7 +12206,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1628</v>
+        <v>2058</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -11592,7 +12384,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1629</v>
+        <v>2059</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11673,7 +12465,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1630</v>
+        <v>2060</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11864,7 +12656,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1631</v>
+        <v>2061</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11954,7 +12746,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1632</v>
+        <v>2062</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12140,7 +12932,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1633</v>
+        <v>2063</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12230,7 +13022,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1634</v>
+        <v>2064</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12416,7 +13208,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1639</v>
+        <v>2069</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12506,7 +13298,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1640</v>
+        <v>2070</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12687,7 +13479,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1635</v>
+        <v>2065</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -12769,7 +13561,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1636</v>
+        <v>2066</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12946,7 +13738,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1637</v>
+        <v>2067</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -13027,7 +13819,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1638</v>
+        <v>2068</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -13218,7 +14010,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1641</v>
+        <v>2071</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -13308,7 +14100,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1642</v>
+        <v>2072</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -13510,7 +14302,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1797</v>
+        <v>1969</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -13593,7 +14385,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1798</v>
+        <v>1970</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -13631,7 +14423,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1799</v>
+        <v>1971</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -13702,7 +14494,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1800</v>
+        <v>1972</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -13785,7 +14577,7 @@
         <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1801</v>
+        <v>1973</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -13823,7 +14615,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1802</v>
+        <v>1974</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -13988,10 +14780,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1751</v>
+        <v>2025</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14047,7 +14839,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1752</v>
+        <v>2026</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -14100,10 +14892,10 @@
     </row>
     <row ht="72" r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1753</v>
+        <v>2027</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -14156,10 +14948,10 @@
     </row>
     <row ht="72" r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1754</v>
+        <v>2028</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -14317,10 +15109,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1679</v>
+        <v>2029</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -14383,10 +15175,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1680</v>
+        <v>2030</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14449,10 +15241,10 @@
     </row>
     <row ht="72" r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1681</v>
+        <v>2031</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -14515,10 +15307,10 @@
     </row>
     <row ht="72" r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1682</v>
+        <v>2032</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -14686,10 +15478,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1683</v>
+        <v>2033</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -14752,10 +15544,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1684</v>
+        <v>2034</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14818,10 +15610,10 @@
     </row>
     <row ht="72" r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1685</v>
+        <v>2035</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -14884,10 +15676,10 @@
     </row>
     <row ht="72" r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1686</v>
+        <v>2036</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -15049,7 +15841,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1671</v>
+        <v>2021</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -15106,7 +15898,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1672</v>
+        <v>2022</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15163,7 +15955,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1673</v>
+        <v>2023</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>68</v>
@@ -15220,7 +16012,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1674</v>
+        <v>2024</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -15378,7 +16170,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1659</v>
+        <v>2089</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -15429,7 +16221,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1660</v>
+        <v>2090</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15582,10 +16374,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1661</v>
+        <v>2091</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -15642,10 +16434,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1662</v>
+        <v>2092</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15807,10 +16599,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1663</v>
+        <v>2093</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -15867,10 +16659,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1664</v>
+        <v>2094</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -16026,7 +16818,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1657</v>
+        <v>2087</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -16076,7 +16868,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1658</v>
+        <v>2088</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -16224,7 +17016,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1645</v>
+        <v>2075</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -16284,7 +17076,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1646</v>
+        <v>2076</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -16451,7 +17243,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1649</v>
+        <v>2079</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16517,7 +17309,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1650</v>
+        <v>2080</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -16704,7 +17496,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1811</v>
+        <v>1983</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16784,7 +17576,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1812</v>
+        <v>1984</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -16822,7 +17614,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1813</v>
+        <v>1985</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>69</v>
@@ -16887,7 +17679,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1814</v>
+        <v>1986</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -16967,7 +17759,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1815</v>
+        <v>1987</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>68</v>
@@ -17005,7 +17797,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1816</v>
+        <v>1988</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>69</v>
@@ -17167,7 +17959,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1647</v>
+        <v>2077</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17224,7 +18016,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1648</v>
+        <v>2078</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -17391,7 +18183,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1651</v>
+        <v>2081</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17457,7 +18249,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1652</v>
+        <v>2082</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -17628,7 +18420,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1656</v>
+        <v>2086</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17799,7 +18591,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1655</v>
+        <v>2085</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17961,7 +18753,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1653</v>
+        <v>2083</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -18117,7 +18909,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1654</v>
+        <v>2084</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -18275,7 +19067,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1623</v>
+        <v>2053</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -18357,7 +19149,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1624</v>
+        <v>2054</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -18538,7 +19330,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1745</v>
+        <v>2055</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -18620,7 +19412,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1746</v>
+        <v>2056</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -18799,7 +19591,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1643</v>
+        <v>2073</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -18852,7 +19644,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1644</v>
+        <v>2074</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -19006,7 +19798,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1609</v>
+        <v>2039</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -19077,7 +19869,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1610</v>
+        <v>2040</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -19244,7 +20036,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1617</v>
+        <v>2047</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -19315,7 +20107,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1618</v>
+        <v>2048</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -19482,10 +20274,10 @@
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1613</v>
+        <v>2043</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -19566,10 +20358,10 @@
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1614</v>
+        <v>2044</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -19749,10 +20541,10 @@
     </row>
     <row ht="57.6" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1621</v>
+        <v>2051</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -19833,10 +20625,10 @@
     </row>
     <row ht="57.6" r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1622</v>
+        <v>2052</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>

--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10419" uniqueCount="2095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10613" uniqueCount="2192">
   <si>
     <t>Result</t>
   </si>
@@ -6356,6 +6356,297 @@
   </si>
   <si>
     <t>Thu Oct 01 05:37:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 06:50:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 06:56:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 06:59:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:02:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:15:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:18:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:21:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:27:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:30:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:32:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:33:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:36:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:38:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:42:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:44:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:46:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:47:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:49:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:51:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:53:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:55:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:57:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 07:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:00:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:02:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:03:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:05:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:07:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:14:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:22:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:29:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:37:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:42:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:45:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:49:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:53:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 08:56:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:00:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:04:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:07:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:12:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:13:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:16:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:17:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:18:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:20:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:21:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:22:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:24:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:25:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:26:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:27:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:28:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:29:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:31:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:34:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:37:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:40:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:43:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:50:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:53:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:15:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:16:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:20:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:06:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:08:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:09:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:12:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:15:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:41:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:42:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:44:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:46:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:47:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:48:36 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -6884,10 +7175,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>2013</v>
+        <v>2145</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6922,10 +7213,10 @@
     </row>
     <row ht="28.8" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>2014</v>
+        <v>2146</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -7002,10 +7293,10 @@
     </row>
     <row ht="28.8" r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>2015</v>
+        <v>2147</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -7085,7 +7376,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>2016</v>
+        <v>2148</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>37</v>
@@ -7150,10 +7441,10 @@
     </row>
     <row ht="28.8" r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>2017</v>
+        <v>2149</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -7191,7 +7482,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>2018</v>
+        <v>2150</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -7268,10 +7559,10 @@
     </row>
     <row ht="28.8" r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>2019</v>
+        <v>2151</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -7351,7 +7642,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>2020</v>
+        <v>2152</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>37</v>
@@ -7519,7 +7810,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2037</v>
+        <v>2169</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -7603,7 +7894,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2038</v>
+        <v>2170</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -7783,7 +8074,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2045</v>
+        <v>2177</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -7862,10 +8153,10 @@
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2046</v>
+        <v>2178</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -8046,7 +8337,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2041</v>
+        <v>2173</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -8130,7 +8421,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2042</v>
+        <v>2174</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -8313,7 +8604,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2049</v>
+        <v>2181</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -8397,7 +8688,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2050</v>
+        <v>2182</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -8574,10 +8865,10 @@
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1979</v>
+        <v>2111</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -8655,10 +8946,10 @@
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1980</v>
+        <v>2112</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -8711,7 +9002,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1981</v>
+        <v>2113</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -8792,7 +9083,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1982</v>
+        <v>2114</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -8946,7 +9237,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1993</v>
+        <v>2125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8997,10 +9288,10 @@
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1994</v>
+        <v>2126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -9082,7 +9373,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1995</v>
+        <v>2127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -9133,10 +9424,10 @@
     </row>
     <row ht="72" r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1996</v>
+        <v>2128</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -9320,7 +9611,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2001</v>
+        <v>2133</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -9407,7 +9698,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2002</v>
+        <v>2134</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -9468,7 +9759,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2003</v>
+        <v>2135</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -9555,7 +9846,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2004</v>
+        <v>2136</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -9718,7 +10009,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2005</v>
+        <v>2137</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -9805,7 +10096,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2006</v>
+        <v>2138</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -9866,7 +10157,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2007</v>
+        <v>2139</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -9953,7 +10244,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2008</v>
+        <v>2140</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -10110,7 +10401,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1989</v>
+        <v>2121</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10164,7 +10455,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1990</v>
+        <v>2122</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -10246,7 +10537,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1991</v>
+        <v>2123</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -10300,7 +10591,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1992</v>
+        <v>2124</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -10475,10 +10766,10 @@
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1975</v>
+        <v>2107</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -10556,10 +10847,10 @@
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1976</v>
+        <v>2108</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -10612,7 +10903,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>1977</v>
+        <v>2109</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -10693,7 +10984,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>1978</v>
+        <v>2110</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -10872,7 +11163,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1963</v>
+        <v>2095</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -10955,7 +11246,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1964</v>
+        <v>2096</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -10993,7 +11284,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1965</v>
+        <v>2097</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -11064,7 +11355,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1966</v>
+        <v>2098</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11147,7 +11438,7 @@
         <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1967</v>
+        <v>2099</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -11185,7 +11476,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1968</v>
+        <v>2100</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -11359,7 +11650,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2009</v>
+        <v>2141</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -11446,7 +11737,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2010</v>
+        <v>2142</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -11507,7 +11798,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2011</v>
+        <v>2143</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -11594,7 +11885,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2012</v>
+        <v>2144</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -12124,7 +12415,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2057</v>
+        <v>2189</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -12206,7 +12497,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2058</v>
+        <v>2190</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -12384,7 +12675,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2059</v>
+        <v>2191</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -14302,7 +14593,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1969</v>
+        <v>2101</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -14385,7 +14676,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1970</v>
+        <v>2102</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -14423,7 +14714,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1971</v>
+        <v>2103</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -14494,7 +14785,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1972</v>
+        <v>2104</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -14577,7 +14868,7 @@
         <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1973</v>
+        <v>2105</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -14615,7 +14906,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1974</v>
+        <v>2106</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -14783,7 +15074,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2025</v>
+        <v>2157</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14836,10 +15127,10 @@
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2026</v>
+        <v>2158</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -14895,7 +15186,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2027</v>
+        <v>2159</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -14951,7 +15242,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2028</v>
+        <v>2160</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -15112,7 +15403,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2029</v>
+        <v>2161</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15178,7 +15469,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2030</v>
+        <v>2162</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15244,7 +15535,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2031</v>
+        <v>2163</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -15310,7 +15601,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2032</v>
+        <v>2164</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -15481,7 +15772,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2033</v>
+        <v>2165</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15547,7 +15838,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2034</v>
+        <v>2166</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15613,7 +15904,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2035</v>
+        <v>2167</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -15679,7 +15970,7 @@
         <v>81</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2036</v>
+        <v>2168</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -15841,7 +16132,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2021</v>
+        <v>2153</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -15895,10 +16186,10 @@
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2022</v>
+        <v>2154</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15952,10 +16243,10 @@
     </row>
     <row ht="43.2" r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>2023</v>
+        <v>2155</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>68</v>
@@ -16012,7 +16303,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>2024</v>
+        <v>2156</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -17496,7 +17787,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>1983</v>
+        <v>2115</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17573,10 +17864,10 @@
     </row>
     <row ht="28.8" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>1984</v>
+        <v>2116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -17614,7 +17905,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>1985</v>
+        <v>2117</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>69</v>
@@ -17679,7 +17970,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>1986</v>
+        <v>2118</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -17756,10 +18047,10 @@
     </row>
     <row ht="28.8" r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>1987</v>
+        <v>2119</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>68</v>
@@ -17794,10 +18085,10 @@
     </row>
     <row ht="43.2" r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s" s="1">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>1988</v>
+        <v>2120</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>69</v>
@@ -19067,7 +19358,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2053</v>
+        <v>2185</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -19149,7 +19440,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2054</v>
+        <v>2186</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -19330,7 +19621,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2055</v>
+        <v>2187</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -19412,7 +19703,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2056</v>
+        <v>2188</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -19798,7 +20089,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2039</v>
+        <v>2171</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -19869,7 +20160,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2040</v>
+        <v>2172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -20033,10 +20324,10 @@
     </row>
     <row ht="115.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2047</v>
+        <v>2179</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -20107,7 +20398,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2048</v>
+        <v>2180</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -20277,7 +20568,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2043</v>
+        <v>2175</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -20361,7 +20652,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2044</v>
+        <v>2176</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -20544,7 +20835,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>2051</v>
+        <v>2183</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -20628,7 +20919,7 @@
         <v>81</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>2052</v>
+        <v>2184</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
